--- a/data/ground_truth/ADMR.xlsx
+++ b/data/ground_truth/ADMR.xlsx
@@ -603,8 +603,10 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>1</v>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>ADMR</t>
+        </is>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
